--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R217eed054d084542"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra722b84621164b93"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra722b84621164b93"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6feee27d73684d8f"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6feee27d73684d8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R493f443a0a024604"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R493f443a0a024604"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re4de9f19619545b7"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Re4de9f19619545b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R063f5cd2d6d94fee"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R063f5cd2d6d94fee"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab002abb8e20498a"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rab002abb8e20498a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4328d22749441ad"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra4328d22749441ad"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d8e878683244172"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4d8e878683244172"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf64a8af72fe046ed"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf64a8af72fe046ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe229c35ae4a41b9"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfe229c35ae4a41b9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd2f7700cca54a07"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbd2f7700cca54a07"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcd4b1fa3b23a4bf5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcd4b1fa3b23a4bf5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce4d4155d7a846d5"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rce4d4155d7a846d5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf7079c80b7f409e"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdf7079c80b7f409e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfcf0e2f750b944b4"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rfcf0e2f750b944b4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb52d4987e2d94168"/>
   </x:sheets>
 </x:workbook>
 </file>

--- a/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/DataValidation_Custom/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb52d4987e2d94168"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R17b2a1572f8f4c12"/>
   </x:sheets>
 </x:workbook>
 </file>
